--- a/artfynd/A 22633-2026 artfynd.xlsx
+++ b/artfynd/A 22633-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>75305330</v>
+        <v>90516089</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96313</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>530</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Hårklomossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dichelyma capillaceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L. ex Dicks.) Myrin</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Alsterån Blomstermåla, Sm</t>
+          <t>Karlsfors, 1500 meter SO, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579034.1855860769</v>
+        <v>579100</v>
       </c>
       <c r="R2" t="n">
-        <v>6316812.03468567</v>
+        <v>6316775</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-05-22</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-05-22</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,21 +759,127 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Granskog med inslagna ek, björk och asp.</t>
+          <t>vattendrag</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Ola Hammarström</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering/funktionsklassning Kalmar län</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>75305330</v>
+      </c>
+      <c r="B3" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Alsterån Blomstermåla, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>579034</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6316812</v>
+      </c>
+      <c r="S3" t="n">
+        <v>100</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2018-05-22</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2018-05-22</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Granskog med inslagna ek, björk och asp.</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Petter Bohman</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Petter Bohman</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t>Lövskogsinventering Kalmar 2018</t>
         </is>

--- a/artfynd/A 22633-2026 artfynd.xlsx
+++ b/artfynd/A 22633-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Naturvärdesinventering/funktionsklassning Kalmar län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90516089</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,8 +894,17 @@
           <t>Lövskogsinventering Kalmar 2018</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75305330</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>